--- a/6758.T_report.xlsx
+++ b/6758.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,58 +449,914 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-01-06</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2909.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2804.23</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1964</v>
+      </c>
+      <c r="I2" t="n">
+        <v>961705</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-01-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2022-01-19</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2822.47</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2407.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1782</v>
+      </c>
+      <c r="I3" t="n">
+        <v>818529</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2265.37</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2286.23</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1645</v>
+      </c>
+      <c r="I4" t="n">
+        <v>824419</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-7.73%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2377.33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2418.62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1663</v>
+      </c>
+      <c r="I5" t="n">
+        <v>837075</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>12.2日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2480.39</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2688.01</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1744</v>
+      </c>
+      <c r="I6" t="n">
+        <v>905396</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>922735</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2605.05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2639.03</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1823</v>
+      </c>
+      <c r="I7" t="n">
+        <v>915383</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>-77265</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2603.63</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2517.84</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1801</v>
+      </c>
+      <c r="I8" t="n">
+        <v>883421</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>37174</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2727.71</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2908.98</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1826</v>
+      </c>
+      <c r="I9" t="n">
+        <v>940305</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2901.06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2797.64</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1847</v>
+      </c>
+      <c r="I10" t="n">
+        <v>904936</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2856.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2743.67</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I11" t="n">
+        <v>867492</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2896.41</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3137.03</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1807</v>
+      </c>
+      <c r="I12" t="n">
+        <v>937754</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3422.94</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3666.47</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1942</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1002529</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3750.16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3590.27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1962</v>
+      </c>
+      <c r="I14" t="n">
+        <v>957823</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3808.61</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3661.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1879</v>
+      </c>
+      <c r="I15" t="n">
+        <v>918849</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3560.07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3779.17</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1894</v>
+      </c>
+      <c r="I16" t="n">
+        <v>973504</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3798.67</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3717.66</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1926</v>
+      </c>
+      <c r="I17" t="n">
+        <v>950817</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3837.44</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4097.66</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1966</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1013326</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4046.21</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4051.03</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1012504</v>
+      </c>
+      <c r="J19" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4242.06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4118.96</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1996</v>
+      </c>
+      <c r="I20" t="n">
+        <v>981127</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4655.46</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4387.43</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1906</v>
+      </c>
+      <c r="I21" t="n">
+        <v>922735</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
         </is>
       </c>
     </row>

--- a/6758.T_report.xlsx
+++ b/6758.T_report.xlsx
@@ -589,29 +589,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2265.37</v>
       </c>
       <c r="E4" t="n">
-        <v>2286.23</v>
+        <v>2285.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="G4" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="I4" t="n">
-        <v>824419</v>
+        <v>824067</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-7.73%</t>
+          <t>-7.77%</t>
         </is>
       </c>
     </row>
@@ -656,10 +656,10 @@
         <v>1.54</v>
       </c>
       <c r="H5" t="n">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="I5" t="n">
-        <v>837075</v>
+        <v>836718</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12.2日</t>
+          <t>12.3日</t>
         </is>
       </c>
     </row>
@@ -707,10 +707,10 @@
         <v>8.16</v>
       </c>
       <c r="H6" t="n">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="I6" t="n">
-        <v>905396</v>
+        <v>905010</v>
       </c>
       <c r="J6" t="n">
         <v>9</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>922735</v>
+        <v>922341</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="I7" t="n">
-        <v>915383</v>
+        <v>914992</v>
       </c>
       <c r="J7" t="n">
         <v>27</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-77265</v>
+        <v>-77659</v>
       </c>
     </row>
     <row r="8">
@@ -805,10 +805,10 @@
         <v>-3.49</v>
       </c>
       <c r="H8" t="n">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="I8" t="n">
-        <v>883421</v>
+        <v>883044</v>
       </c>
       <c r="J8" t="n">
         <v>12</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>37174</v>
+        <v>37160</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>6.44</v>
       </c>
       <c r="H9" t="n">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="I9" t="n">
-        <v>940305</v>
+        <v>939904</v>
       </c>
       <c r="J9" t="n">
         <v>12</v>
@@ -895,10 +895,10 @@
         <v>-3.76</v>
       </c>
       <c r="H10" t="n">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="I10" t="n">
-        <v>904936</v>
+        <v>904550</v>
       </c>
       <c r="J10" t="n">
         <v>6</v>
@@ -936,10 +936,10 @@
         <v>-4.14</v>
       </c>
       <c r="H11" t="n">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="I11" t="n">
-        <v>867492</v>
+        <v>867122</v>
       </c>
       <c r="J11" t="n">
         <v>9</v>
@@ -977,10 +977,10 @@
         <v>8.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="I12" t="n">
-        <v>937754</v>
+        <v>937353</v>
       </c>
       <c r="J12" t="n">
         <v>22</v>
@@ -1018,10 +1018,10 @@
         <v>6.91</v>
       </c>
       <c r="H13" t="n">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="I13" t="n">
-        <v>1002529</v>
+        <v>1002101</v>
       </c>
       <c r="J13" t="n">
         <v>15</v>
@@ -1059,10 +1059,10 @@
         <v>-4.46</v>
       </c>
       <c r="H14" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="I14" t="n">
-        <v>957823</v>
+        <v>957414</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
@@ -1100,10 +1100,10 @@
         <v>-4.07</v>
       </c>
       <c r="H15" t="n">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="I15" t="n">
-        <v>918849</v>
+        <v>918456</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -1141,10 +1141,10 @@
         <v>5.95</v>
       </c>
       <c r="H16" t="n">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="I16" t="n">
-        <v>973504</v>
+        <v>973088</v>
       </c>
       <c r="J16" t="n">
         <v>20</v>
@@ -1182,10 +1182,10 @@
         <v>-2.33</v>
       </c>
       <c r="H17" t="n">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="I17" t="n">
-        <v>950817</v>
+        <v>950411</v>
       </c>
       <c r="J17" t="n">
         <v>14</v>
@@ -1223,10 +1223,10 @@
         <v>6.57</v>
       </c>
       <c r="H18" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="I18" t="n">
-        <v>1013326</v>
+        <v>1012893</v>
       </c>
       <c r="J18" t="n">
         <v>6</v>
@@ -1264,10 +1264,10 @@
         <v>-0.08</v>
       </c>
       <c r="H19" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="I19" t="n">
-        <v>1012504</v>
+        <v>1012071</v>
       </c>
       <c r="J19" t="n">
         <v>15</v>
@@ -1305,10 +1305,10 @@
         <v>-3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="I20" t="n">
-        <v>981127</v>
+        <v>980708</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
@@ -1346,10 +1346,10 @@
         <v>-5.95</v>
       </c>
       <c r="H21" t="n">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="I21" t="n">
-        <v>922735</v>
+        <v>922341</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
